--- a/data/agricultural_experience_facility/data.xlsx
+++ b/data/agricultural_experience_facility/data.xlsx
@@ -472,7 +472,7 @@
         <v>16:00</v>
       </c>
       <c r="L2" t="str">
-        <v>水曜日が祝日の場合は、その日以降の平日が休日となる。また、１２月２９日から１月３日までは休業日となる。</v>
+        <v>定休日：水曜日（祝日と重なった場合、変更の可能性あり。）、お盆休み、年末年始（期間は年によって異なります。）</v>
       </c>
     </row>
   </sheetData>
